--- a/downloads/food.xlsx
+++ b/downloads/food.xlsx
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L812"/>
+  <dimension ref="A1:L848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -36179,7 +36179,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F699" t="n">
@@ -36227,7 +36227,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F700" t="n">
@@ -36275,7 +36275,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F701" t="n">
@@ -36323,7 +36323,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F702" t="n">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F703" t="n">
@@ -36419,7 +36419,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F704" t="n">
@@ -36467,7 +36467,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F705" t="n">
@@ -36515,7 +36515,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F706" t="n">
@@ -36563,7 +36563,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F707" t="n">
@@ -36611,7 +36611,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F708" t="n">
@@ -36659,7 +36659,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F709" t="n">
@@ -36707,7 +36707,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F710" t="n">
@@ -36755,7 +36755,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F711" t="n">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F712" t="n">
@@ -36851,7 +36851,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F713" t="n">
@@ -36899,7 +36899,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F714" t="n">
@@ -36947,7 +36947,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F715" t="n">
@@ -36995,7 +36995,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F716" t="n">
@@ -37043,7 +37043,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F717" t="n">
@@ -37091,7 +37091,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F718" t="n">
@@ -37139,7 +37139,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F719" t="n">
@@ -37187,7 +37187,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F720" t="n">
@@ -37235,7 +37235,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F721" t="n">
@@ -37283,7 +37283,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F722" t="n">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F723" t="n">
@@ -37364,32 +37364,32 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>מונג אדולט אקטיב עוף 12 ק"ג</t>
+          <t>*מונג וט כלב יורנרי סטרוויט 2 ק"ג * חדש</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>29000237</t>
+          <t>29000359</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F724" t="n">
-        <v>318</v>
+        <v>116</v>
       </c>
       <c r="G724" t="n">
-        <v>375.24</v>
+        <v>136.88</v>
       </c>
       <c r="H724">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I724">
@@ -37397,11 +37397,11 @@
         <v/>
       </c>
       <c r="J724">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K724">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L724">
@@ -37412,32 +37412,32 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>מונג אדולט ארנב אורז ותפוא 12 ק"ג</t>
+          <t>*מונג וט כלב יורנרי סטרוויט 12 ק"ג * חדש</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>29000125</t>
+          <t>29000360</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F725" t="n">
-        <v>318</v>
+        <v>469</v>
       </c>
       <c r="G725" t="n">
-        <v>375.24</v>
+        <v>553.42</v>
       </c>
       <c r="H725">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I725">
@@ -37445,11 +37445,11 @@
         <v/>
       </c>
       <c r="J725">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K725">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L725">
@@ -37460,32 +37460,32 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>מונג אדולט ארנב אורז ותפוא 2.5 ק"ג</t>
+          <t>מונג וט דרמטוזיס רטוב 150 ג' כלב</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>29000208</t>
+          <t>15170002</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F726" t="n">
-        <v>90</v>
+        <v>6.7</v>
       </c>
       <c r="G726" t="n">
-        <v>106.2</v>
+        <v>7.91</v>
       </c>
       <c r="H726">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I726">
@@ -37493,11 +37493,11 @@
         <v/>
       </c>
       <c r="J726">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K726">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L726">
@@ -37508,32 +37508,32 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>מונג אדולט בקר ואורז 12 ק"ג</t>
+          <t>מונג וט גסטרואינטסטינל רטוב 150 ג' כלב</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>29000303</t>
+          <t>15170003</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F727" t="n">
-        <v>318</v>
+        <v>6.7</v>
       </c>
       <c r="G727" t="n">
-        <v>375.24</v>
+        <v>7.91</v>
       </c>
       <c r="H727">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I727">
@@ -37541,11 +37541,11 @@
         <v/>
       </c>
       <c r="J727">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K727">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L727">
@@ -37556,32 +37556,32 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>מונג אדולט בקר ואורז 2.5 ק"ג</t>
+          <t>מונג וט רנל ואוקסלייט רטוב 150 ג' כלב</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>29000304</t>
+          <t>15170004</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F728" t="n">
-        <v>90</v>
+        <v>6.7</v>
       </c>
       <c r="G728" t="n">
-        <v>106.2</v>
+        <v>7.91</v>
       </c>
       <c r="H728">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I728">
@@ -37589,11 +37589,11 @@
         <v/>
       </c>
       <c r="J728">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K728">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L728">
@@ -37604,32 +37604,32 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>מונג אדולט ברווז אורז ותפוא 12 ק"ג</t>
+          <t>מונג וט ריקברי רטוב 150 ג' כלב</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>29000124</t>
+          <t>15170005</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F729" t="n">
-        <v>318</v>
+        <v>7.9</v>
       </c>
       <c r="G729" t="n">
-        <v>375.24</v>
+        <v>9.32</v>
       </c>
       <c r="H729">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I729">
@@ -37637,11 +37637,11 @@
         <v/>
       </c>
       <c r="J729">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K729">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L729">
@@ -37652,32 +37652,32 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>מונג אדולט ברווז אורז ותפוא 2.5 ק"ג</t>
+          <t>מונג וט דרמטוזיס רטוב 100 ג' חתול</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>29000207</t>
+          <t>15170006</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F730" t="n">
-        <v>90</v>
+        <v>5.4</v>
       </c>
       <c r="G730" t="n">
-        <v>106.2</v>
+        <v>6.37</v>
       </c>
       <c r="H730">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I730">
@@ -37685,11 +37685,11 @@
         <v/>
       </c>
       <c r="J730">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K730">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L730">
@@ -37700,32 +37700,32 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>מונג אדולט חזיר אורז ותפוא 12 ק"ג</t>
+          <t>מונג וט גסטרואינטסטינל רטוב 100 ג' חתול</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>29000222</t>
+          <t>15170007</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F731" t="n">
-        <v>318</v>
+        <v>5.4</v>
       </c>
       <c r="G731" t="n">
-        <v>375.24</v>
+        <v>6.37</v>
       </c>
       <c r="H731">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I731">
@@ -37733,11 +37733,11 @@
         <v/>
       </c>
       <c r="J731">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K731">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L731">
@@ -37748,32 +37748,32 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>מונג אדולט חזיר אורז ותפוא 2.5 ק"ג</t>
+          <t>מונג וט יורינרי סטרוויט רטוב 100 ג' חתול</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>29000218</t>
+          <t>15170008</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F732" t="n">
-        <v>90</v>
+        <v>5.4</v>
       </c>
       <c r="G732" t="n">
-        <v>106.2</v>
+        <v>6.37</v>
       </c>
       <c r="H732">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I732">
@@ -37781,11 +37781,11 @@
         <v/>
       </c>
       <c r="J732">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K732">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L732">
@@ -37796,32 +37796,32 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>מונג אדולט כבש אורז ותפוא 12 ק"ג</t>
+          <t>מונג וט רנל ואוקסלייט רטוב 100 ג' חתול</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>29000163</t>
+          <t>15170009</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F733" t="n">
-        <v>318</v>
+        <v>5.4</v>
       </c>
       <c r="G733" t="n">
-        <v>375.24</v>
+        <v>6.37</v>
       </c>
       <c r="H733">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I733">
@@ -37829,11 +37829,11 @@
         <v/>
       </c>
       <c r="J733">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K733">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L733">
@@ -37844,32 +37844,32 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>מונג אדולט כבש אורז ותפוא 2.5 ק"ג</t>
+          <t>מונג וט ריקברי רטוב 100 ג' חתול</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>29000211</t>
+          <t>15170010</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F734" t="n">
-        <v>90</v>
+        <v>5.9</v>
       </c>
       <c r="G734" t="n">
-        <v>106.2</v>
+        <v>6.96</v>
       </c>
       <c r="H734">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I734">
@@ -37877,11 +37877,11 @@
         <v/>
       </c>
       <c r="J734">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K734">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L734">
@@ -37892,32 +37892,32 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>מונג אדולט סלמון ואורז 12 ק"ג</t>
+          <t>מונג וט גסטרואינטסטינל פחית 400 ג' (12 במגש)</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>29000162</t>
+          <t>15170050</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F735" t="n">
-        <v>318</v>
+        <v>12</v>
       </c>
       <c r="G735" t="n">
-        <v>375.24</v>
+        <v>14.16</v>
       </c>
       <c r="H735">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I735">
@@ -37925,11 +37925,11 @@
         <v/>
       </c>
       <c r="J735">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K735">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L735">
@@ -37940,32 +37940,32 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>מונג אדולט סלמון ואורז 2.5 ק"ג</t>
+          <t>מונג וט היפו מונו ברווז פחית 400 ג' (12 במגש)</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>29000210</t>
+          <t>15170052</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F736" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="G736" t="n">
-        <v>106.2</v>
+        <v>14.16</v>
       </c>
       <c r="H736">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I736">
@@ -37973,11 +37973,11 @@
         <v/>
       </c>
       <c r="J736">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K736">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L736">
@@ -37988,32 +37988,32 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>מונג אדולט סלמון ואורז לייט 12 ק"ג</t>
+          <t>מונג וט היפו מונו חזיר פחית 400 ג' (12 במגש)</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>29000145</t>
+          <t>15170053</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F737" t="n">
-        <v>318</v>
+        <v>12</v>
       </c>
       <c r="G737" t="n">
-        <v>375.24</v>
+        <v>14.16</v>
       </c>
       <c r="H737">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I737">
@@ -38021,11 +38021,11 @@
         <v/>
       </c>
       <c r="J737">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K737">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L737">
@@ -38036,32 +38036,32 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>מונג אדולט סלמון ואורז לייט 2.5 ק"ג</t>
+          <t>מונג וט היפו מונו טונה פחית 400 ג' (12 במגש)</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>29000223</t>
+          <t>15170051</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F738" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="G738" t="n">
-        <v>106.2</v>
+        <v>14.16</v>
       </c>
       <c r="H738">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I738">
@@ -38069,11 +38069,11 @@
         <v/>
       </c>
       <c r="J738">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K738">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L738">
@@ -38084,32 +38084,32 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>Monge Vet Solution</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>מונג אדולט סלמון וטונה היפו 12 ק"ג</t>
+          <t>מונג וט היפו מונו כבש פחית 400 ג' (12 במגש)</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>29000126</t>
+          <t>15170049</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F739" t="n">
-        <v>318</v>
+        <v>12</v>
       </c>
       <c r="G739" t="n">
-        <v>375.24</v>
+        <v>14.16</v>
       </c>
       <c r="H739">
-        <f>הגדרות!B10</f>
+        <f>הגדרות!B9</f>
         <v/>
       </c>
       <c r="I739">
@@ -38117,11 +38117,11 @@
         <v/>
       </c>
       <c r="J739">
-        <f>הגדרות!C10</f>
+        <f>הגדרות!C9</f>
         <v/>
       </c>
       <c r="K739">
-        <f>הגדרות!D10</f>
+        <f>הגדרות!D9</f>
         <v/>
       </c>
       <c r="L739">
@@ -38137,24 +38137,24 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>מונג אדולט סלמון וטונה היפו 2.5 ק"ג</t>
+          <t>מונג אדולט אקטיב עוף 12 ק"ג</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>29000172</t>
+          <t>29000237</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F740" t="n">
-        <v>90</v>
+        <v>318</v>
       </c>
       <c r="G740" t="n">
-        <v>106.2</v>
+        <v>375.24</v>
       </c>
       <c r="H740">
         <f>הגדרות!B10</f>
@@ -38185,17 +38185,17 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>מונג אדולט עוף אורז ותפוא 12 ק"ג</t>
+          <t>מונג אדולט ארנב אורז ותפוא 12 ק"ג</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>29000300</t>
+          <t>29000125</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F741" t="n">
@@ -38233,17 +38233,17 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>מונג אדולט עוף אורז ותפוא 2.5 ק"ג</t>
+          <t>מונג אדולט ארנב אורז ותפוא 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>29000299</t>
+          <t>29000208</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F742" t="n">
@@ -38281,17 +38281,17 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>מונג אדולט פורל אורז ותפוא 12 ק"ג</t>
+          <t>מונג אדולט בקר ואורז 12 ק"ג</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>29000295</t>
+          <t>29000303</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F743" t="n">
@@ -38329,17 +38329,17 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>מונג אדולט פורל אורז ותפוא 2.5 ק"ג</t>
+          <t>מונג אדולט בקר ואורז 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>29000296</t>
+          <t>29000304</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F744" t="n">
@@ -38377,24 +38377,24 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>מונג אקס סמול אדולט 3 ק"ג</t>
+          <t>מונג אדולט ברווז אורז ותפוא 12 ק"ג</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>29000107</t>
+          <t>29000124</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F745" t="n">
-        <v>100</v>
+        <v>318</v>
       </c>
       <c r="G745" t="n">
-        <v>118</v>
+        <v>375.24</v>
       </c>
       <c r="H745">
         <f>הגדרות!B10</f>
@@ -38425,24 +38425,24 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>מונג אקס סמול אדולט 800 גרם</t>
+          <t>מונג אדולט ברווז אורז ותפוא 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>29000347</t>
+          <t>29000207</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G746" t="n">
-        <v>43.66</v>
+        <v>106.2</v>
       </c>
       <c r="H746">
         <f>הגדרות!B10</f>
@@ -38473,24 +38473,24 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>מונג אקס סמול אדולט כבש אורז ותפוא 2.5 ק"ג</t>
+          <t>מונג אדולט חזיר אורז ותפוא 12 ק"ג</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>29000109</t>
+          <t>29000222</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F747" t="n">
-        <v>89</v>
+        <v>318</v>
       </c>
       <c r="G747" t="n">
-        <v>105.02</v>
+        <v>375.24</v>
       </c>
       <c r="H747">
         <f>הגדרות!B10</f>
@@ -38521,24 +38521,24 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>מונג אקס סמול אדולט כבש אורז ותפוא 800 גרם</t>
+          <t>מונג אדולט חזיר אורז ותפוא 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>29000266</t>
+          <t>29000218</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F748" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G748" t="n">
-        <v>47.2</v>
+        <v>106.2</v>
       </c>
       <c r="H748">
         <f>הגדרות!B10</f>
@@ -38569,24 +38569,24 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>מונג אקס סמול אדולט סלמון ואורז 2.5 ק"ג</t>
+          <t>מונג אדולט כבש אורז ותפוא 12 ק"ג</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>29000108</t>
+          <t>29000163</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F749" t="n">
-        <v>89</v>
+        <v>318</v>
       </c>
       <c r="G749" t="n">
-        <v>105.02</v>
+        <v>375.24</v>
       </c>
       <c r="H749">
         <f>הגדרות!B10</f>
@@ -38617,24 +38617,24 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>מונג אקס סמול פפי 800 גרם</t>
+          <t>מונג אדולט כבש אורז ותפוא 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>29000225</t>
+          <t>29000211</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F750" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G750" t="n">
-        <v>43.66</v>
+        <v>106.2</v>
       </c>
       <c r="H750">
         <f>הגדרות!B10</f>
@@ -38665,24 +38665,24 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>מונג חתול אדולט ארנב 1.5 ק"ג</t>
+          <t>מונג אדולט סלמון ואורז 12 ק"ג</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>29000244</t>
+          <t>29000162</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F751" t="n">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="G751" t="n">
-        <v>90.86</v>
+        <v>375.24</v>
       </c>
       <c r="H751">
         <f>הגדרות!B10</f>
@@ -38713,24 +38713,24 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>מונג חתול אדולט עוף 1.5 ק"ג</t>
+          <t>מונג אדולט סלמון ואורז 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>29000165</t>
+          <t>29000210</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F752" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G752" t="n">
-        <v>90.86</v>
+        <v>106.2</v>
       </c>
       <c r="H752">
         <f>הגדרות!B10</f>
@@ -38761,24 +38761,24 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>מונג חתול אדולט עוף 10 ק"ג</t>
+          <t>מונג אדולט סלמון ואורז לייט 12 ק"ג</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>29000231</t>
+          <t>29000145</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F753" t="n">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="G753" t="n">
-        <v>348.1</v>
+        <v>375.24</v>
       </c>
       <c r="H753">
         <f>הגדרות!B10</f>
@@ -38809,24 +38809,24 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>מונג חתול אינדור עוף 1.5 ק"ג</t>
+          <t>מונג אדולט סלמון ואורז לייט 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>29000166</t>
+          <t>29000223</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F754" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G754" t="n">
-        <v>90.86</v>
+        <v>106.2</v>
       </c>
       <c r="H754">
         <f>הגדרות!B10</f>
@@ -38857,24 +38857,24 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>מונג חתול אינדור עוף 10 ק"ג</t>
+          <t>מונג אדולט סלמון וטונה היפו 12 ק"ג</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>29000232</t>
+          <t>29000126</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F755" t="n">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="G755" t="n">
-        <v>348.1</v>
+        <v>375.24</v>
       </c>
       <c r="H755">
         <f>הגדרות!B10</f>
@@ -38905,24 +38905,24 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>מונג חתול היירבול עוף 1.5 ק"ג</t>
+          <t>מונג אדולט סלמון וטונה היפו 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>29000131</t>
+          <t>29000172</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F756" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G756" t="n">
-        <v>90.86</v>
+        <v>106.2</v>
       </c>
       <c r="H756">
         <f>הגדרות!B10</f>
@@ -38953,24 +38953,24 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>מונג חתול היירבול עוף 10 ק"ג</t>
+          <t>מונג אדולט עוף אורז ותפוא 12 ק"ג</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>29000230</t>
+          <t>29000300</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F757" t="n">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="G757" t="n">
-        <v>348.1</v>
+        <v>375.24</v>
       </c>
       <c r="H757">
         <f>הגדרות!B10</f>
@@ -39001,24 +39001,24 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>מונג חתול יורינרי 1.5 ק"ג</t>
+          <t>מונג אדולט עוף אורז ותפוא 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>29000164</t>
+          <t>29000299</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F758" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G758" t="n">
-        <v>90.86</v>
+        <v>106.2</v>
       </c>
       <c r="H758">
         <f>הגדרות!B10</f>
@@ -39049,24 +39049,24 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>מונג חתול יורינרי 10 ק"ג</t>
+          <t>מונג אדולט פורל אורז ותפוא 12 ק"ג</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>29000175</t>
+          <t>29000295</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F759" t="n">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="G759" t="n">
-        <v>397.66</v>
+        <v>375.24</v>
       </c>
       <c r="H759">
         <f>הגדרות!B10</f>
@@ -39097,24 +39097,24 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>מונג חתול לייט הודו 1.5 ק"ג</t>
+          <t>מונג אדולט פורל אורז ותפוא 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>29000301</t>
+          <t>29000296</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F760" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G760" t="n">
-        <v>90.86</v>
+        <v>106.2</v>
       </c>
       <c r="H760">
         <f>הגדרות!B10</f>
@@ -39145,24 +39145,24 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>מונג חתול מונו אדולט סטרילייז בקר 1.5 ק"ג</t>
+          <t>מונג אקס סמול אדולט 3 ק"ג</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>29000297</t>
+          <t>29000107</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F761" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="G761" t="n">
-        <v>90.86</v>
+        <v>118</v>
       </c>
       <c r="H761">
         <f>הגדרות!B10</f>
@@ -39193,24 +39193,24 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>מונג חתול מונו אדולט סטרילייז ברווז 1.5 ק"ג</t>
+          <t>מונג אקס סמול אדולט כבש אורז ותפוא 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>29000240</t>
+          <t>29000109</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F762" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G762" t="n">
-        <v>90.86</v>
+        <v>105.02</v>
       </c>
       <c r="H762">
         <f>הגדרות!B10</f>
@@ -39241,24 +39241,24 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>מונג חתול מונו אדולט סטרילייז דג בקלה 1.5 ק"ג</t>
+          <t>מונג אקס סמול אדולט סלמון ואורז 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>29000298</t>
+          <t>29000108</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F763" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G763" t="n">
-        <v>90.86</v>
+        <v>105.02</v>
       </c>
       <c r="H763">
         <f>הגדרות!B10</f>
@@ -39289,17 +39289,17 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>מונג חתול מונו אדולט סלמון 1.5 ק"ג</t>
+          <t>מונג חתול אדולט ארנב 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>29000243</t>
+          <t>29000244</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F764" t="n">
@@ -39337,17 +39337,17 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>מונג חתול מונו סטרילייז פורל 1.5 ק"ג</t>
+          <t>מונג חתול אדולט עוף 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>29000241</t>
+          <t>29000165</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F765" t="n">
@@ -39385,24 +39385,24 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>מונג חתול מונו קיטן פורל 1.5 ק"ג</t>
+          <t>מונג חתול אדולט עוף 10 ק"ג</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>29000242</t>
+          <t>29000231</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F766" t="n">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="G766" t="n">
-        <v>90.86</v>
+        <v>348.1</v>
       </c>
       <c r="H766">
         <f>הגדרות!B10</f>
@@ -39433,17 +39433,17 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>מונג חתול סטרילייז 1.5 ק"ג</t>
+          <t>מונג חתול אינדור עוף 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>29000129</t>
+          <t>29000166</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F767" t="n">
@@ -39481,24 +39481,24 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>מונג חתול סטרילייז 10 ק"ג</t>
+          <t>מונג חתול אינדור עוף 10 ק"ג</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>29000156</t>
+          <t>29000232</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F768" t="n">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="G768" t="n">
-        <v>336.3</v>
+        <v>348.1</v>
       </c>
       <c r="H768">
         <f>הגדרות!B10</f>
@@ -39529,24 +39529,24 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>מונג חתול סטרילייז 400 גרם</t>
+          <t>מונג חתול היירבול עוף 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>29000265</t>
+          <t>29000131</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F769" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="G769" t="n">
-        <v>38.94</v>
+        <v>90.86</v>
       </c>
       <c r="H769">
         <f>הגדרות!B10</f>
@@ -39577,24 +39577,24 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>מונג חתול סניור 1.5 ק"ג</t>
+          <t>מונג חתול היירבול עוף 10 ק"ג</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>29000294</t>
+          <t>29000230</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F770" t="n">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="G770" t="n">
-        <v>90.86</v>
+        <v>348.1</v>
       </c>
       <c r="H770">
         <f>הגדרות!B10</f>
@@ -39625,24 +39625,24 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>מונג חתול סנסטיב עוף 10 ק"ג</t>
+          <t>מונג חתול יורינרי 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>29000233</t>
+          <t>29000164</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F771" t="n">
-        <v>302</v>
+        <v>77</v>
       </c>
       <c r="G771" t="n">
-        <v>356.36</v>
+        <v>90.86</v>
       </c>
       <c r="H771">
         <f>הגדרות!B10</f>
@@ -39673,24 +39673,24 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>מונג חתול קיטן בקר 1.5 ק"ג</t>
+          <t>מונג חתול יורינרי 10 ק"ג</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>29000314</t>
+          <t>29000175</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F772" t="n">
-        <v>77</v>
+        <v>337</v>
       </c>
       <c r="G772" t="n">
-        <v>90.86</v>
+        <v>397.66</v>
       </c>
       <c r="H772">
         <f>הגדרות!B10</f>
@@ -39721,17 +39721,17 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>מונג חתול קיטן ברווז 1.5 ק"ג</t>
+          <t>מונג חתול לייט הודו 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>29000315</t>
+          <t>29000301</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F773" t="n">
@@ -39769,17 +39769,17 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>מונג חתול קיטן עוף 1.5 ק"ג</t>
+          <t>מונג חתול מונו אדולט סטרילייז בקר 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>29000130</t>
+          <t>29000297</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F774" t="n">
@@ -39817,24 +39817,24 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>מונג חתול קיטן עוף 10 ק"ג</t>
+          <t>מונג חתול מונו אדולט סטרילייז ברווז 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>29000157</t>
+          <t>29000240</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F775" t="n">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="G775" t="n">
-        <v>336.3</v>
+        <v>90.86</v>
       </c>
       <c r="H775">
         <f>הגדרות!B10</f>
@@ -39865,24 +39865,24 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>מונג חתול קיטן עוף 400 גרם</t>
+          <t>מונג חתול סטרילייז ברווז 10 ק"ג</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>29000200</t>
+          <t>29000365</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F776" t="n">
-        <v>33</v>
+        <v>333</v>
       </c>
       <c r="G776" t="n">
-        <v>38.94</v>
+        <v>392.94</v>
       </c>
       <c r="H776">
         <f>הגדרות!B10</f>
@@ -39913,24 +39913,24 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>מונג מדיום אדולט 12 ק"ג כלב</t>
+          <t>מונג חתול מונו אדולט סטרילייז דג בקלה 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>29000117</t>
+          <t>29000298</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F777" t="n">
-        <v>270</v>
+        <v>77</v>
       </c>
       <c r="G777" t="n">
-        <v>318.6</v>
+        <v>90.86</v>
       </c>
       <c r="H777">
         <f>הגדרות!B10</f>
@@ -39961,24 +39961,24 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>מונג מדיום אדולט 3 ק"ג</t>
+          <t>מונג חתול מונו אדולט סלמון 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>29000283</t>
+          <t>29000243</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F778" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="G778" t="n">
-        <v>125.08</v>
+        <v>90.86</v>
       </c>
       <c r="H778">
         <f>הגדרות!B10</f>
@@ -40009,24 +40009,24 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>מונג מדיום סטרטר 1.5 ק"ג</t>
+          <t>מונג חתול מונו סטרילייז פורל 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>29000281</t>
+          <t>29000241</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F779" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="G779" t="n">
-        <v>67.26000000000001</v>
+        <v>90.86</v>
       </c>
       <c r="H779">
         <f>הגדרות!B10</f>
@@ -40057,24 +40057,24 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>מונג מדיום סניור 12 ק"ג כלב</t>
+          <t>מונג חתול מונו קיטן פורל 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>29000115</t>
+          <t>29000242</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F780" t="n">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="G780" t="n">
-        <v>335.12</v>
+        <v>90.86</v>
       </c>
       <c r="H780">
         <f>הגדרות!B10</f>
@@ -40105,24 +40105,24 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>מונג מדיום סניור 3 ק"ג</t>
+          <t>מונג חתול סטרילייז 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>29000282</t>
+          <t>29000129</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F781" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="G781" t="n">
-        <v>132.16</v>
+        <v>90.86</v>
       </c>
       <c r="H781">
         <f>הגדרות!B10</f>
@@ -40153,24 +40153,24 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>מונג מדיום פפי 12 ק"ג כלב</t>
+          <t>מונג חתול סטרילייז 10 ק"ג</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>29000116</t>
+          <t>29000156</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F782" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G782" t="n">
-        <v>335.12</v>
+        <v>336.3</v>
       </c>
       <c r="H782">
         <f>הגדרות!B10</f>
@@ -40201,24 +40201,24 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>מונג מדיום פפי 3 ק"ג כלב</t>
+          <t>מונג חתול סניור 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>29000120</t>
+          <t>29000294</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F783" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="G783" t="n">
-        <v>132.16</v>
+        <v>90.86</v>
       </c>
       <c r="H783">
         <f>הגדרות!B10</f>
@@ -40249,24 +40249,24 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>מונג מדיום פפי 800 גרם</t>
+          <t>מונג חתול סנסטיב עוף 10 ק"ג</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>29000196</t>
+          <t>29000233</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F784" t="n">
-        <v>37</v>
+        <v>302</v>
       </c>
       <c r="G784" t="n">
-        <v>43.66</v>
+        <v>356.36</v>
       </c>
       <c r="H784">
         <f>הגדרות!B10</f>
@@ -40297,24 +40297,24 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט 3 ק"ג</t>
+          <t>מונג חתול קיטן בקר 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>29000209</t>
+          <t>29000314</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F785" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="G785" t="n">
-        <v>116.82</v>
+        <v>90.86</v>
       </c>
       <c r="H785">
         <f>הגדרות!B10</f>
@@ -40345,24 +40345,24 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט 800 גרם</t>
+          <t>מונג חתול קיטן ברווז 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>29000199</t>
+          <t>29000315</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F786" t="n">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="G786" t="n">
-        <v>43.66</v>
+        <v>90.86</v>
       </c>
       <c r="H786">
         <f>הגדרות!B10</f>
@@ -40393,24 +40393,24 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט כבש אורז ותפוא 2.5 ק"ג כלב</t>
+          <t>מונג חתול קיטן עוף 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>29000111</t>
+          <t>29000130</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F787" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="G787" t="n">
-        <v>118</v>
+        <v>90.86</v>
       </c>
       <c r="H787">
         <f>הגדרות!B10</f>
@@ -40441,24 +40441,24 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט כבש אורז ותפוא 7.5 ק"ג כלב</t>
+          <t>מונג חתול קיטן עוף 10 ק"ג</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>29000112</t>
+          <t>29000157</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F788" t="n">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="G788" t="n">
-        <v>263.14</v>
+        <v>336.3</v>
       </c>
       <c r="H788">
         <f>הגדרות!B10</f>
@@ -40489,24 +40489,24 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט כבש אורז ותפוא 800 גרם</t>
+          <t>מונג מדיום אדולט 12 ק"ג כלב</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>29000235</t>
+          <t>29000117</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F789" t="n">
-        <v>40</v>
+        <v>270</v>
       </c>
       <c r="G789" t="n">
-        <v>47.2</v>
+        <v>318.6</v>
       </c>
       <c r="H789">
         <f>הגדרות!B10</f>
@@ -40537,24 +40537,24 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט סלמון ואורז 2.5 ק"ג</t>
+          <t>מונג מדיום אדולט 3 ק"ג</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>29000226</t>
+          <t>29000283</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F790" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G790" t="n">
-        <v>118</v>
+        <v>125.08</v>
       </c>
       <c r="H790">
         <f>הגדרות!B10</f>
@@ -40585,24 +40585,24 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט סלמון ואורז 7.5 ק"ג כלב</t>
+          <t>מונג מדיום סטרטר 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>29000113</t>
+          <t>29000281</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F791" t="n">
-        <v>223</v>
+        <v>57</v>
       </c>
       <c r="G791" t="n">
-        <v>263.14</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="H791">
         <f>הגדרות!B10</f>
@@ -40633,24 +40633,24 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט סלמון ואורז 800 גרם</t>
+          <t>מונג מדיום סניור 12 ק"ג כלב</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>29000195</t>
+          <t>29000115</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F792" t="n">
-        <v>37</v>
+        <v>284</v>
       </c>
       <c r="G792" t="n">
-        <v>43.66</v>
+        <v>335.12</v>
       </c>
       <c r="H792">
         <f>הגדרות!B10</f>
@@ -40681,24 +40681,24 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>מונג מיני אדולט עוף 7.5 ק"ג כלב</t>
+          <t>מונג מדיום סניור 3 ק"ג</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>29000119</t>
+          <t>29000282</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F793" t="n">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="G793" t="n">
-        <v>223.02</v>
+        <v>132.16</v>
       </c>
       <c r="H793">
         <f>הגדרות!B10</f>
@@ -40729,24 +40729,24 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>מונג מיני סטרטר 1.5 ק"ג</t>
+          <t>מונג מדיום פפי 12 ק"ג כלב</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>29000221</t>
+          <t>29000116</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F794" t="n">
-        <v>63</v>
+        <v>284</v>
       </c>
       <c r="G794" t="n">
-        <v>74.34</v>
+        <v>335.12</v>
       </c>
       <c r="H794">
         <f>הגדרות!B10</f>
@@ -40777,17 +40777,17 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>מונג מיני סניור 3 ק"ג כלב</t>
+          <t>מונג מדיום פפי 3 ק"ג כלב</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>29000114</t>
+          <t>29000120</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F795" t="n">
@@ -40825,24 +40825,24 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>מונג מיני פפי גוניור 800 גרם</t>
+          <t>מונג מיני אדולט 3 ק"ג</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>29000198</t>
+          <t>29000209</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F796" t="n">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="G796" t="n">
-        <v>43.66</v>
+        <v>116.82</v>
       </c>
       <c r="H796">
         <f>הגדרות!B10</f>
@@ -40873,17 +40873,17 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>מונג מיני פפי כבש ואורז 2.5 ק"ג כלב</t>
+          <t>מונג מיני אדולט כבש אורז ותפוא 2.5 ק"ג כלב</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>29000110</t>
+          <t>29000111</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F797" t="n">
@@ -40921,24 +40921,24 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>מונג מיני פפי כבש ואורז 800 גרם</t>
+          <t>מונג מיני אדולט כבש אורז ותפוא 7.5 ק"ג כלב</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>29000234</t>
+          <t>29000112</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F798" t="n">
-        <v>40</v>
+        <v>223</v>
       </c>
       <c r="G798" t="n">
-        <v>47.2</v>
+        <v>263.14</v>
       </c>
       <c r="H798">
         <f>הגדרות!B10</f>
@@ -40969,24 +40969,24 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>מונג מיני פפי עוף 3 ק"ג</t>
+          <t>מונג מיני אדולט סלמון ואורז 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>29000220</t>
+          <t>29000226</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F799" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G799" t="n">
-        <v>132.16</v>
+        <v>118</v>
       </c>
       <c r="H799">
         <f>הגדרות!B10</f>
@@ -41017,24 +41017,24 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>מונג מקסי אדולט 12 ק"ג כלב</t>
+          <t>מונג מיני אדולט סלמון ואורז 7.5 ק"ג כלב</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>29000118</t>
+          <t>29000113</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F800" t="n">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="G800" t="n">
-        <v>325.68</v>
+        <v>263.14</v>
       </c>
       <c r="H800">
         <f>הגדרות!B10</f>
@@ -41065,24 +41065,24 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>מונג מקסי פפי 12 ק"ג</t>
+          <t>מונג מיני אדולט עוף 7.5 ק"ג כלב</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>29000146</t>
+          <t>29000119</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F801" t="n">
-        <v>284</v>
+        <v>189</v>
       </c>
       <c r="G801" t="n">
-        <v>335.12</v>
+        <v>223.02</v>
       </c>
       <c r="H801">
         <f>הגדרות!B10</f>
@@ -41113,24 +41113,24 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>מונג מקסי פפי 800 גרם</t>
+          <t>מונג מיני סטרטר 1.5 ק"ג</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>29000197</t>
+          <t>29000221</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F802" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="G802" t="n">
-        <v>43.66</v>
+        <v>74.34</v>
       </c>
       <c r="H802">
         <f>הגדרות!B10</f>
@@ -41161,24 +41161,24 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>מונג פפי ברווז אורז ותפוא 2.5 ק"ג</t>
+          <t>מונג מיני סניור 3 ק"ג כלב</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>29000318</t>
+          <t>29000114</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F803" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G803" t="n">
-        <v>121.54</v>
+        <v>132.16</v>
       </c>
       <c r="H803">
         <f>הגדרות!B10</f>
@@ -41209,24 +41209,24 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>מונג פפי ברווז ותפוח אדמה 12 ק"ג</t>
+          <t>מונג מיני פפי כבש ואורז 2.5 ק"ג כלב</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>29000344</t>
+          <t>29000110</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>318</v>
+        <v>100</v>
       </c>
       <c r="G804" t="n">
-        <v>375.24</v>
+        <v>118</v>
       </c>
       <c r="H804">
         <f>הגדרות!B10</f>
@@ -41257,24 +41257,24 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>מונג פפי כבש ואורז 12 ק"ג</t>
+          <t>מונג מיני פפי עוף 3 ק"ג</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>29000127</t>
+          <t>29000220</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F805" t="n">
-        <v>318</v>
+        <v>112</v>
       </c>
       <c r="G805" t="n">
-        <v>375.24</v>
+        <v>132.16</v>
       </c>
       <c r="H805">
         <f>הגדרות!B10</f>
@@ -41305,24 +41305,24 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>מונג פפי כבש ואורז 2.5 ק"ג</t>
+          <t>מונג מקסי אדולט 12 ק"ג כלב</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>29000224</t>
+          <t>29000118</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F806" t="n">
-        <v>90</v>
+        <v>276</v>
       </c>
       <c r="G806" t="n">
-        <v>106.2</v>
+        <v>325.68</v>
       </c>
       <c r="H806">
         <f>הגדרות!B10</f>
@@ -41353,24 +41353,24 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>מונג פפי כבש ואורז 800 גרם</t>
+          <t>מונג מקסי פפי 12 ק"ג</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>29000193</t>
+          <t>29000146</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F807" t="n">
-        <v>37</v>
+        <v>284</v>
       </c>
       <c r="G807" t="n">
-        <v>43.66</v>
+        <v>335.12</v>
       </c>
       <c r="H807">
         <f>הגדרות!B10</f>
@@ -41401,24 +41401,24 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>מונג פפי סלמון ואורז 12 ק"ג</t>
+          <t>מונג פפי ברווז אורז ותפוא 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>29000128</t>
+          <t>29000318</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F808" t="n">
-        <v>318</v>
+        <v>103</v>
       </c>
       <c r="G808" t="n">
-        <v>375.24</v>
+        <v>121.54</v>
       </c>
       <c r="H808">
         <f>הגדרות!B10</f>
@@ -41449,24 +41449,24 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>מונג פפי סלמון ואורז 2.5 ק"ג</t>
+          <t>מונג פפי ברווז ותפוח אדמה 12 ק"ג</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>29000219</t>
+          <t>29000344</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F809" t="n">
-        <v>90</v>
+        <v>318</v>
       </c>
       <c r="G809" t="n">
-        <v>106.2</v>
+        <v>375.24</v>
       </c>
       <c r="H809">
         <f>הגדרות!B10</f>
@@ -41497,24 +41497,24 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>מונג פפי סלמון ואורז 800 גרם</t>
+          <t>מונג פפי כבש ואורז 12 ק"ג</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>29000194</t>
+          <t>29000127</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F810" t="n">
-        <v>37</v>
+        <v>318</v>
       </c>
       <c r="G810" t="n">
-        <v>43.66</v>
+        <v>375.24</v>
       </c>
       <c r="H810">
         <f>הגדרות!B10</f>
@@ -41545,24 +41545,24 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>מונג פפי פורל אורז ותפו"א 2.5 ק"ג</t>
+          <t>מונג פפי כבש ואורז 2.5 ק"ג</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>29000343</t>
+          <t>29000224</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G811" t="n">
-        <v>121.54</v>
+        <v>106.2</v>
       </c>
       <c r="H811">
         <f>הגדרות!B10</f>
@@ -41593,17 +41593,17 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>מונג פפי פורל ותפו"א 12 ק"ג</t>
+          <t>מונג פפי סלמון ואורז 12 ק"ג</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>29000345</t>
+          <t>29000128</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F812" t="n">
@@ -41630,6 +41630,1889 @@
       </c>
       <c r="L812">
         <f>I812*(1+J812/100)+K812</f>
+        <v/>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>מונג פפי סלמון ואורז 2.5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>29000219</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F813" t="n">
+        <v>90</v>
+      </c>
+      <c r="G813" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="H813">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I813">
+        <f>F813*(1-H813/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J813">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K813">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L813">
+        <f>I813*(1+J813/100)+K813</f>
+        <v/>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>מונג פפי פורל אורז ותפו"א 2.5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>29000343</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F814" t="n">
+        <v>103</v>
+      </c>
+      <c r="G814" t="n">
+        <v>121.54</v>
+      </c>
+      <c r="H814">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I814">
+        <f>F814*(1-H814/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J814">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K814">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L814">
+        <f>I814*(1+J814/100)+K814</f>
+        <v/>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>מונג פפי פורל ותפו"א 12 ק"ג</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>29000345</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F815" t="n">
+        <v>318</v>
+      </c>
+      <c r="G815" t="n">
+        <v>375.24</v>
+      </c>
+      <c r="H815">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I815">
+        <f>F815*(1-H815/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J815">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K815">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L815">
+        <f>I815*(1+J815/100)+K815</f>
+        <v/>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>מונג פפי חזיר אורז ותפוא 2.5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>29000358</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F816" t="n">
+        <v>90</v>
+      </c>
+      <c r="G816" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="H816">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I816">
+        <f>F816*(1-H816/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J816">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K816">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L816">
+        <f>I816*(1+J816/100)+K816</f>
+        <v/>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>מונג מיני פפי סלמון ואורז 2.5 ק"ג כלב</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>29000357</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F817" t="n">
+        <v>100</v>
+      </c>
+      <c r="G817" t="n">
+        <v>118</v>
+      </c>
+      <c r="H817">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I817">
+        <f>F817*(1-H817/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J817">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K817">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L817">
+        <f>I817*(1+J817/100)+K817</f>
+        <v/>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי אדולט בופלו תפוא 1.5 ק"ג * חתול BW</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>29000276</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F818" t="n">
+        <v>86</v>
+      </c>
+      <c r="G818" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="H818">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I818">
+        <f>F818*(1-H818/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J818">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K818">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L818">
+        <f>I818*(1+J818/100)+K818</f>
+        <v/>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי אדולט בקלה תפוא 1.5 ק"ג * חתול BW</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>29000275</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F819" t="n">
+        <v>86</v>
+      </c>
+      <c r="G819" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="H819">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I819">
+        <f>F819*(1-H819/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J819">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K819">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L819">
+        <f>I819*(1+J819/100)+K819</f>
+        <v/>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי אדולט סלמון ואפונה 1.5 ק"ג * חתול BW</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>29000277</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F820" t="n">
+        <v>86</v>
+      </c>
+      <c r="G820" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="H820">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I820">
+        <f>F820*(1-H820/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J820">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K820">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L820">
+        <f>I820*(1+J820/100)+K820</f>
+        <v/>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי אדולט סלמון ואפונה 12 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>29000273</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F821" t="n">
+        <v>449</v>
+      </c>
+      <c r="G821" t="n">
+        <v>529.8200000000001</v>
+      </c>
+      <c r="H821">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I821">
+        <f>F821*(1-H821/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J821">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K821">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L821">
+        <f>I821*(1+J821/100)+K821</f>
+        <v/>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי אדולט סלמון ואפונה 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>29000286</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F822" t="n">
+        <v>130</v>
+      </c>
+      <c r="G822" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="H822">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I822">
+        <f>F822*(1-H822/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J822">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K822">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L822">
+        <f>I822*(1+J822/100)+K822</f>
+        <v/>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי אנשובי תפוא ואפונה 2.5 ק"ג</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>29000176</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F823" t="n">
+        <v>130</v>
+      </c>
+      <c r="G823" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="H823">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I823">
+        <f>F823*(1-H823/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J823">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K823">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L823">
+        <f>I823*(1+J823/100)+K823</f>
+        <v/>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי ברווז ותפוא 12 ק"ג * כלב B.W</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>29000123</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F824" t="n">
+        <v>449</v>
+      </c>
+      <c r="G824" t="n">
+        <v>529.8200000000001</v>
+      </c>
+      <c r="H824">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I824">
+        <f>F824*(1-H824/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J824">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K824">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L824">
+        <f>I824*(1+J824/100)+K824</f>
+        <v/>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי ברווז ותפוח אדמה 2.5 ק"ג * כלב B.W</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>29000177</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F825" t="n">
+        <v>120</v>
+      </c>
+      <c r="G825" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="H825">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I825">
+        <f>F825*(1-H825/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J825">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K825">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L825">
+        <f>I825*(1+J825/100)+K825</f>
+        <v/>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי כבש תפוא אפונה 12 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>29000267</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F826" t="n">
+        <v>449</v>
+      </c>
+      <c r="G826" t="n">
+        <v>529.8200000000001</v>
+      </c>
+      <c r="H826">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I826">
+        <f>F826*(1-H826/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J826">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K826">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L826">
+        <f>I826*(1+J826/100)+K826</f>
+        <v/>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי כבש תפוא אפונה 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>29000287</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F827" t="n">
+        <v>130</v>
+      </c>
+      <c r="G827" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="H827">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I827">
+        <f>F827*(1-H827/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J827">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K827">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L827">
+        <f>I827*(1+J827/100)+K827</f>
+        <v/>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי כלב אנשובי תפוא ואפונה 12 ק"ג</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>29000122</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F828" t="n">
+        <v>449</v>
+      </c>
+      <c r="G828" t="n">
+        <v>529.8200000000001</v>
+      </c>
+      <c r="H828">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I828">
+        <f>F828*(1-H828/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J828">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K828">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L828">
+        <f>I828*(1+J828/100)+K828</f>
+        <v/>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי מיני אד. ברווז תפוא 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>29000280</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F829" t="n">
+        <v>130</v>
+      </c>
+      <c r="G829" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="H829">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I829">
+        <f>F829*(1-H829/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J829">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K829">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L829">
+        <f>I829*(1+J829/100)+K829</f>
+        <v/>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי מיני אנשובי ואפונה 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>29000288</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F830" t="n">
+        <v>150</v>
+      </c>
+      <c r="G830" t="n">
+        <v>177</v>
+      </c>
+      <c r="H830">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I830">
+        <f>F830*(1-H830/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J830">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K830">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L830">
+        <f>I830*(1+J830/100)+K830</f>
+        <v/>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי סטריליז טונה ואפונה 1.5 ק"ג * חתול BW</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>29000278</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F831" t="n">
+        <v>86</v>
+      </c>
+      <c r="G831" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="H831">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I831">
+        <f>F831*(1-H831/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J831">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K831">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L831">
+        <f>I831*(1+J831/100)+K831</f>
+        <v/>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי פפי ברווז ותפוא 12 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>29000268</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F832" t="n">
+        <v>449</v>
+      </c>
+      <c r="G832" t="n">
+        <v>529.8200000000001</v>
+      </c>
+      <c r="H832">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I832">
+        <f>F832*(1-H832/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J832">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K832">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L832">
+        <f>I832*(1+J832/100)+K832</f>
+        <v/>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>מונג ג.פרי פפי ברווז ותפוא 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>29000279</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F833" t="n">
+        <v>130</v>
+      </c>
+      <c r="G833" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="H833">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I833">
+        <f>F833*(1-H833/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J833">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K833">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L833">
+        <f>I833*(1+J833/100)+K833</f>
+        <v/>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>מונג חתול ביווילד 1.5 ק"ג אנשובי BW</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>29000106</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F834" t="n">
+        <v>86</v>
+      </c>
+      <c r="G834" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="H834">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I834">
+        <f>F834*(1-H834/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J834">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K834">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L834">
+        <f>I834*(1+J834/100)+K834</f>
+        <v/>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>מונג חתול ביווילד 1.5 ק"ג ארנבת BW</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>29000105</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F835" t="n">
+        <v>86</v>
+      </c>
+      <c r="G835" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="H835">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I835">
+        <f>F835*(1-H835/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J835">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K835">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L835">
+        <f>I835*(1+J835/100)+K835</f>
+        <v/>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>מונג חתול ביווילד אנשובי 10 ק"ג BW</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>29000228</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F836" t="n">
+        <v>421</v>
+      </c>
+      <c r="G836" t="n">
+        <v>496.78</v>
+      </c>
+      <c r="H836">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I836">
+        <f>F836*(1-H836/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J836">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K836">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L836">
+        <f>I836*(1+J836/100)+K836</f>
+        <v/>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>מונג חתול ביווילד ארנבת 10 ק"ג BW</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>29000229</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F837" t="n">
+        <v>421</v>
+      </c>
+      <c r="G837" t="n">
+        <v>496.78</v>
+      </c>
+      <c r="H837">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I837">
+        <f>F837*(1-H837/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J837">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K837">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L837">
+        <f>I837*(1+J837/100)+K837</f>
+        <v/>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>מונג חתול ל.גריין קיטן אווז 1.5 ק"ג * BW</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>29000274</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F838" t="n">
+        <v>90</v>
+      </c>
+      <c r="G838" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="H838">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I838">
+        <f>F838*(1-H838/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J838">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K838">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L838">
+        <f>I838*(1+J838/100)+K838</f>
+        <v/>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>מונג חתול לארג בופלו 10 ק"ג BW</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>29000302</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F839" t="n">
+        <v>421</v>
+      </c>
+      <c r="G839" t="n">
+        <v>496.78</v>
+      </c>
+      <c r="H839">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I839">
+        <f>F839*(1-H839/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J839">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K839">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L839">
+        <f>I839*(1+J839/100)+K839</f>
+        <v/>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>מונג חתול קיטן אווז 10 ק"ג BW</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>29000309</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F840" t="n">
+        <v>421</v>
+      </c>
+      <c r="G840" t="n">
+        <v>496.78</v>
+      </c>
+      <c r="H840">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I840">
+        <f>F840*(1-H840/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J840">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K840">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L840">
+        <f>I840*(1+J840/100)+K840</f>
+        <v/>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>מונג ל.גריין אדולט אווז 12 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>29000270</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F841" t="n">
+        <v>348</v>
+      </c>
+      <c r="G841" t="n">
+        <v>410.64</v>
+      </c>
+      <c r="H841">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I841">
+        <f>F841*(1-H841/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J841">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K841">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L841">
+        <f>I841*(1+J841/100)+K841</f>
+        <v/>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>מונג ל.גריין אדולט אווז 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>29000292</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F842" t="n">
+        <v>113</v>
+      </c>
+      <c r="G842" t="n">
+        <v>133.34</v>
+      </c>
+      <c r="H842">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I842">
+        <f>F842*(1-H842/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J842">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K842">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L842">
+        <f>I842*(1+J842/100)+K842</f>
+        <v/>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>מונג ל.גריין אדולט חזיר בר 12 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>29000269</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F843" t="n">
+        <v>348</v>
+      </c>
+      <c r="G843" t="n">
+        <v>410.64</v>
+      </c>
+      <c r="H843">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I843">
+        <f>F843*(1-H843/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J843">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K843">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L843">
+        <f>I843*(1+J843/100)+K843</f>
+        <v/>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>מונג ל.גריין אדולט חזיר בר 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>29000291</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F844" t="n">
+        <v>113</v>
+      </c>
+      <c r="G844" t="n">
+        <v>133.34</v>
+      </c>
+      <c r="H844">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I844">
+        <f>F844*(1-H844/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J844">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K844">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L844">
+        <f>I844*(1+J844/100)+K844</f>
+        <v/>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>מונג ל.גריין אדולט צבי 12 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>29000271</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F845" t="n">
+        <v>396</v>
+      </c>
+      <c r="G845" t="n">
+        <v>467.28</v>
+      </c>
+      <c r="H845">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I845">
+        <f>F845*(1-H845/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J845">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K845">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L845">
+        <f>I845*(1+J845/100)+K845</f>
+        <v/>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>מונג ל.גריין אדולט צבי 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>29000290</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F846" t="n">
+        <v>113</v>
+      </c>
+      <c r="G846" t="n">
+        <v>133.34</v>
+      </c>
+      <c r="H846">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I846">
+        <f>F846*(1-H846/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J846">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K846">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L846">
+        <f>I846*(1+J846/100)+K846</f>
+        <v/>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>מונג ל.גריין פפי צבי 12 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>29000272</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F847" t="n">
+        <v>401</v>
+      </c>
+      <c r="G847" t="n">
+        <v>473.18</v>
+      </c>
+      <c r="H847">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I847">
+        <f>F847*(1-H847/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J847">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K847">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L847">
+        <f>I847*(1+J847/100)+K847</f>
+        <v/>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Monge</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>מונג ל.גריין פפי צבי 2.5 ק"ג * כלב BW</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>BeWild</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>29000289</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F848" t="n">
+        <v>113</v>
+      </c>
+      <c r="G848" t="n">
+        <v>133.34</v>
+      </c>
+      <c r="H848">
+        <f>הגדרות!B10</f>
+        <v/>
+      </c>
+      <c r="I848">
+        <f>F848*(1-H848/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J848">
+        <f>הגדרות!C10</f>
+        <v/>
+      </c>
+      <c r="K848">
+        <f>הגדרות!D10</f>
+        <v/>
+      </c>
+      <c r="L848">
+        <f>I848*(1+J848/100)+K848</f>
         <v/>
       </c>
     </row>
